--- a/zhiyinlou_race_test_latest.xlsx
+++ b/zhiyinlou_race_test_latest.xlsx
@@ -15,6 +15,7 @@
     <sheet name="测试小班赛跑J2" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="测试小班游泳J3" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="测试小班游泳J1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="国际新小班暑J10跑酷赛跑" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4260,4 +4261,485 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>题目序号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>音频命名</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>题干图片</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>选项序号</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>选项图片名称</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>选项文本内容</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>是否正确</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑音频单词book</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑book</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑bag</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑toy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑音频单词bag</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑toy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑bag</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑book</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑音频单词toy</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑bag</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑book</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑toy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑音频单词toy</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑toy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑book</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑bag</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑音频单词book</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑book</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑bag</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑toy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑音频单词bag</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑bag</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑book</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑toy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑音频单词book</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑toy</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑bag</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑book</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑音频单词toy</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑bag</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑toy</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑book</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑音频单词bag</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑bag</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑book</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑toy</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑音频单词book</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑toy</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑book</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>26暑国际小班10赛跑bag</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>